--- a/newui_Greyform/TERRAHL2-FP-MB-T1am(JMB)_out.xlsx
+++ b/newui_Greyform/TERRAHL2-FP-MB-T1am(JMB)_out.xlsx
@@ -430,6 +430,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Marking Type</t>
@@ -517,7 +522,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -554,7 +559,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -571,7 +576,7 @@
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -608,7 +613,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -625,7 +630,7 @@
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -660,7 +665,11 @@
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -673,7 +682,7 @@
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -708,7 +717,11 @@
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -721,7 +734,7 @@
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -760,7 +773,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -777,7 +790,7 @@
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,7 +829,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -833,7 +846,7 @@
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -872,7 +885,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -889,7 +902,7 @@
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -928,7 +941,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -945,7 +958,7 @@
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -984,7 +997,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1001,7 +1014,7 @@
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1040,7 +1053,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1057,7 +1070,7 @@
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1096,7 +1109,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1113,7 +1126,7 @@
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1152,7 +1165,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1169,7 +1182,7 @@
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1208,7 +1221,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1225,7 +1238,7 @@
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1264,7 +1277,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1281,7 +1294,7 @@
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1320,7 +1333,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1337,7 +1350,7 @@
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1376,7 +1389,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1393,7 +1406,7 @@
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1432,7 +1445,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1449,7 +1462,7 @@
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1488,7 +1501,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1505,7 +1518,7 @@
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1544,7 +1557,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1561,7 +1574,7 @@
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1600,7 +1613,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1617,7 +1630,7 @@
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1654,7 +1667,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -1671,7 +1684,7 @@
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1706,7 +1719,11 @@
         <v>2</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -1719,7 +1736,7 @@
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1754,7 +1771,11 @@
         <v>2</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -1767,7 +1788,7 @@
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1806,7 +1827,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -1823,7 +1844,7 @@
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1862,7 +1883,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -1879,7 +1900,7 @@
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1918,7 +1939,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -1935,7 +1956,7 @@
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1974,7 +1995,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -1991,7 +2012,7 @@
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2030,7 +2051,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -2047,7 +2068,7 @@
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2086,7 +2107,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2103,7 +2124,7 @@
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2140,7 +2161,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -2157,7 +2178,7 @@
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2192,7 +2213,11 @@
         <v>3</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
@@ -2205,7 +2230,7 @@
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2240,7 +2265,11 @@
         <v>3</v>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
@@ -2253,7 +2282,7 @@
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2292,7 +2321,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2309,7 +2338,7 @@
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2348,7 +2377,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2365,7 +2394,7 @@
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2404,7 +2433,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2421,7 +2450,7 @@
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2460,7 +2489,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2477,7 +2506,7 @@
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2516,7 +2545,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2533,7 +2562,7 @@
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2572,7 +2601,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2589,7 +2618,7 @@
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2628,7 +2657,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2645,7 +2674,7 @@
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2684,7 +2713,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2701,7 +2730,7 @@
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2738,7 +2767,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -2755,7 +2784,7 @@
       <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2790,7 +2819,11 @@
         <v>4</v>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
@@ -2803,7 +2836,7 @@
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2838,7 +2871,11 @@
         <v>4</v>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
@@ -2851,7 +2888,7 @@
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2890,7 +2927,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2907,7 +2944,7 @@
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2946,7 +2983,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -2963,7 +3000,7 @@
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3002,7 +3039,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -3019,7 +3056,7 @@
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3058,7 +3095,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -3075,7 +3112,7 @@
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3112,7 +3149,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -3129,7 +3166,7 @@
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3164,7 +3201,11 @@
         <v>5</v>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
@@ -3177,7 +3218,7 @@
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3212,7 +3253,11 @@
         <v>5</v>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -3225,7 +3270,7 @@
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3264,7 +3309,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3281,7 +3326,7 @@
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3320,7 +3365,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3337,7 +3382,7 @@
       <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3376,7 +3421,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3393,7 +3438,7 @@
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3430,7 +3475,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3447,7 +3492,7 @@
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3482,7 +3527,11 @@
         <v>6</v>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
@@ -3495,7 +3544,7 @@
       <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3530,7 +3579,11 @@
         <v>6</v>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
@@ -3543,7 +3596,7 @@
       <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3582,7 +3635,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -3599,7 +3652,7 @@
       <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3638,7 +3691,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3655,7 +3708,7 @@
       <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3694,7 +3747,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -3711,7 +3764,7 @@
       <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3750,7 +3803,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -3767,7 +3820,7 @@
       <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3806,7 +3859,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -3823,7 +3876,7 @@
       <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3862,7 +3915,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -3879,7 +3932,7 @@
       <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3918,7 +3971,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -3935,7 +3988,7 @@
       <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3974,7 +4027,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -3991,7 +4044,7 @@
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4041,7 +4094,7 @@
       <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4091,7 +4144,7 @@
       <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4141,7 +4194,7 @@
       <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4191,7 +4244,7 @@
       <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4241,7 +4294,7 @@
       <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4291,7 +4344,7 @@
       <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4341,7 +4394,7 @@
       <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4399,7 +4452,7 @@
       <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4457,7 +4510,7 @@
       <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4515,7 +4568,7 @@
       <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4573,7 +4626,7 @@
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4631,7 +4684,7 @@
       <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4689,7 +4742,7 @@
       <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4747,7 +4800,7 @@
       <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4805,7 +4858,7 @@
       <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4863,7 +4916,7 @@
       <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4921,7 +4974,7 @@
       <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4979,7 +5032,7 @@
       <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5037,7 +5090,7 @@
       <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5095,7 +5148,7 @@
       <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5153,7 +5206,7 @@
       <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5211,7 +5264,7 @@
       <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5269,7 +5322,7 @@
       <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5327,7 +5380,7 @@
       <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5385,7 +5438,7 @@
       <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5443,7 +5496,7 @@
       <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5515,6 +5568,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Marking Type</t>
@@ -5602,7 +5660,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
@@ -5639,7 +5697,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -5656,7 +5714,7 @@
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
@@ -5693,7 +5751,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -5710,7 +5768,7 @@
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
@@ -5747,7 +5805,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -5764,7 +5822,7 @@
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="n">
@@ -5801,7 +5859,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -5818,7 +5876,7 @@
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="n">
@@ -5855,7 +5913,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -5872,7 +5930,7 @@
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="n">
@@ -5909,7 +5967,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -5926,7 +5984,7 @@
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="n">
@@ -5963,7 +6021,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -5980,7 +6038,7 @@
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="n">
@@ -6017,7 +6075,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>done</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -6034,7 +6092,7 @@
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="n">
@@ -6090,7 +6148,7 @@
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="n">

--- a/newui_Greyform/TERRAHL2-FP-MB-T1am(JMB)_out.xlsx
+++ b/newui_Greyform/TERRAHL2-FP-MB-T1am(JMB)_out.xlsx
@@ -430,11 +430,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Marking Type</t>
@@ -522,7 +517,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -559,7 +554,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -576,7 +571,7 @@
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -613,7 +608,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -630,7 +625,7 @@
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -665,11 +660,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -682,7 +673,7 @@
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,11 +708,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -734,7 +721,7 @@
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +760,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -790,7 +777,7 @@
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,7 +816,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -846,7 +833,7 @@
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -885,7 +872,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -902,7 +889,7 @@
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -941,7 +928,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -958,7 +945,7 @@
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -997,7 +984,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1014,7 +1001,7 @@
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1053,7 +1040,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1070,7 +1057,7 @@
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1109,7 +1096,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1126,7 +1113,7 @@
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1165,7 +1152,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1182,7 +1169,7 @@
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1221,7 +1208,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1238,7 +1225,7 @@
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1277,7 +1264,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1294,7 +1281,7 @@
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1333,7 +1320,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1350,7 +1337,7 @@
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1389,7 +1376,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1406,7 +1393,7 @@
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1445,7 +1432,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1462,7 +1449,7 @@
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1501,7 +1488,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1518,7 +1505,7 @@
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1557,7 +1544,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1574,7 +1561,7 @@
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,7 +1600,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1630,7 +1617,7 @@
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1667,7 +1654,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -1684,7 +1671,7 @@
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1719,11 +1706,7 @@
         <v>2</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
@@ -1736,7 +1719,7 @@
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1771,11 +1754,7 @@
         <v>2</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
@@ -1788,7 +1767,7 @@
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1827,7 +1806,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -1844,7 +1823,7 @@
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1883,7 +1862,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -1900,7 +1879,7 @@
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1939,7 +1918,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -1956,7 +1935,7 @@
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1995,7 +1974,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -2012,7 +1991,7 @@
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2051,7 +2030,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -2068,7 +2047,7 @@
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2107,7 +2086,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2124,7 +2103,7 @@
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2161,7 +2140,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -2178,7 +2157,7 @@
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2213,11 +2192,7 @@
         <v>3</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
@@ -2230,7 +2205,7 @@
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2265,11 +2240,7 @@
         <v>3</v>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
@@ -2282,7 +2253,7 @@
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2321,7 +2292,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2338,7 +2309,7 @@
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2377,7 +2348,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2394,7 +2365,7 @@
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2433,7 +2404,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2450,7 +2421,7 @@
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2489,7 +2460,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2506,7 +2477,7 @@
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2545,7 +2516,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2562,7 +2533,7 @@
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="1" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2601,7 +2572,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M39" t="n">
@@ -2618,7 +2589,7 @@
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="1" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2657,7 +2628,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2674,7 +2645,7 @@
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2713,7 +2684,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2730,7 +2701,7 @@
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="1" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2767,7 +2738,7 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -2784,7 +2755,7 @@
       <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="1" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2819,11 +2790,7 @@
         <v>4</v>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
@@ -2836,7 +2803,7 @@
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="1" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2871,11 +2838,7 @@
         <v>4</v>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
@@ -2888,7 +2851,7 @@
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="1" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2927,7 +2890,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2944,7 +2907,7 @@
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="1" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2983,7 +2946,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3000,7 +2963,7 @@
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="1" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3039,7 +3002,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -3056,7 +3019,7 @@
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3095,7 +3058,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -3112,7 +3075,7 @@
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="1" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3149,7 +3112,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -3166,7 +3129,7 @@
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3201,11 +3164,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
@@ -3218,7 +3177,7 @@
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="1" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3253,11 +3212,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
@@ -3270,7 +3225,7 @@
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="1" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3309,7 +3264,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3326,7 +3281,7 @@
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="1" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3365,7 +3320,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3382,7 +3337,7 @@
       <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="1" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3421,7 +3376,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3438,7 +3393,7 @@
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3475,7 +3430,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3492,7 +3447,7 @@
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="1" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3527,11 +3482,7 @@
         <v>6</v>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
@@ -3544,7 +3495,7 @@
       <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="1" t="n">
         <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3579,11 +3530,7 @@
         <v>6</v>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
@@ -3596,7 +3543,7 @@
       <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="1" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3635,7 +3582,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -3652,7 +3599,7 @@
       <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="1" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3691,7 +3638,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3708,7 +3655,7 @@
       <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="1" t="n">
         <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3747,7 +3694,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -3764,7 +3711,7 @@
       <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="1" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3803,7 +3750,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -3820,7 +3767,7 @@
       <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="1" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3859,7 +3806,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -3876,7 +3823,7 @@
       <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="1" t="n">
         <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3915,7 +3862,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -3932,7 +3879,7 @@
       <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="1" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3971,7 +3918,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -3988,7 +3935,7 @@
       <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="1" t="n">
         <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -4027,7 +3974,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -4044,7 +3991,7 @@
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="1" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4094,7 +4041,7 @@
       <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="1" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4144,7 +4091,7 @@
       <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="1" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4194,7 +4141,7 @@
       <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="1" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4244,7 +4191,7 @@
       <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="1" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4294,7 +4241,7 @@
       <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="1" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4344,7 +4291,7 @@
       <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="1" t="n">
         <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4394,7 +4341,7 @@
       <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="1" t="n">
         <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4452,7 +4399,7 @@
       <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="1" t="n">
         <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4510,7 +4457,7 @@
       <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="1" t="n">
         <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4568,7 +4515,7 @@
       <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="1" t="n">
         <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4626,7 +4573,7 @@
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="1" t="n">
         <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4684,7 +4631,7 @@
       <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="1" t="n">
         <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4742,7 +4689,7 @@
       <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="1" t="n">
         <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4800,7 +4747,7 @@
       <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="1" t="n">
         <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4858,7 +4805,7 @@
       <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="1" t="n">
         <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4916,7 +4863,7 @@
       <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="1" t="n">
         <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4974,7 +4921,7 @@
       <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="1" t="n">
         <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -5032,7 +4979,7 @@
       <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="1" t="n">
         <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5090,7 +5037,7 @@
       <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="1" t="n">
         <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5148,7 +5095,7 @@
       <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="1" t="n">
         <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5206,7 +5153,7 @@
       <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="1" t="n">
         <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5264,7 +5211,7 @@
       <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="1" t="n">
         <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5322,7 +5269,7 @@
       <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="1" t="n">
         <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5380,7 +5327,7 @@
       <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" s="1" t="n">
         <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5438,7 +5385,7 @@
       <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" s="1" t="n">
         <v>90</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5496,7 +5443,7 @@
       <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" s="1" t="n">
         <v>91</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5568,11 +5515,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Marking Type</t>
@@ -5660,7 +5602,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
@@ -5697,7 +5639,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -5714,7 +5656,7 @@
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
@@ -5751,7 +5693,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -5768,7 +5710,7 @@
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
@@ -5805,7 +5747,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -5822,7 +5764,7 @@
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="n">
@@ -5859,7 +5801,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -5876,7 +5818,7 @@
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="n">
@@ -5913,7 +5855,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -5930,7 +5872,7 @@
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="n">
@@ -5967,7 +5909,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -5984,7 +5926,7 @@
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="n">
@@ -6021,7 +5963,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -6038,7 +5980,7 @@
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="n">
@@ -6075,7 +6017,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -6092,7 +6034,7 @@
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="n">
@@ -6148,7 +6090,7 @@
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="n">
